--- a/data/trans_orig/P70C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023</t>
+          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132554</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172649</t>
+          <t>172702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109149</t>
+          <t>110289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141946</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252163</t>
+          <t>253654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301831</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>82745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40135</t>
+          <t>40340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61802</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136565</t>
+          <t>134036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52170</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79612</t>
+          <t>78670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40014</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70653</t>
+          <t>69392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63838</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126394</t>
+          <t>124954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41460</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56441</t>
+          <t>54790</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56343</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86918</t>
+          <t>87772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>47407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102043</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141154</t>
+          <t>143142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74467</t>
+          <t>73913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100412</t>
+          <t>101876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189499</t>
+          <t>185923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237808</t>
+          <t>234226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78329</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>39298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60822</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>92680</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129709</t>
+          <t>130430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53656</t>
+          <t>53165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>84112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58977</t>
+          <t>58610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25314</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44770</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>63891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94833</t>
+          <t>94482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43127</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>50691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52398</t>
+          <t>54169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85138</t>
+          <t>85749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131273</t>
+          <t>132187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>443458</t>
+          <t>444284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149045</t>
+          <t>151569</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>489577</t>
+          <t>470102</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>109150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13335</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132848</t>
+          <t>132091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>55597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68921</t>
+          <t>67297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108866</t>
+          <t>108880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104258</t>
+          <t>102991</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66141</t>
+          <t>68405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83222</t>
+          <t>80374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52455</t>
+          <t>52219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109174</t>
+          <t>113245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155626</t>
+          <t>157573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>103356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194377</t>
+          <t>193767</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247899</t>
+          <t>248798</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73956</t>
+          <t>73832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126196</t>
+          <t>122455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66605</t>
+          <t>66883</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95180</t>
+          <t>95092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>151153</t>
+          <t>149432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206215</t>
+          <t>203654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87317</t>
+          <t>87030</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>37376</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>61429</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>101853</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>141049</t>
+          <t>138768</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99495</t>
+          <t>99356</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144078</t>
+          <t>144915</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65536</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93764</t>
+          <t>95050</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>173041</t>
+          <t>171399</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226370</t>
+          <t>224677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79686</t>
+          <t>80062</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125299</t>
+          <t>122654</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>70646</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>103295</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>162282</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>215543</t>
+          <t>210385</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>57765</t>
+          <t>56423</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34303</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>56394</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69189</t>
+          <t>70010</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104808</t>
+          <t>105559</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46638</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79088</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>74277</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>251310</t>
+          <t>253424</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>142002</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>345799</t>
+          <t>338616</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>58265</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>119287</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>57144</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>78083</t>
+          <t>77840</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68202</t>
+          <t>66408</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105661</t>
+          <t>105973</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38967</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>69428</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>65446</t>
+          <t>64811</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>123097</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>72797</t>
+          <t>70902</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>89771</t>
+          <t>91530</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4695,107 +4695,107 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>787110</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607615</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1178983</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>530</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471933</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>398202</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627415</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1259044</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1047256</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1788035</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -4808,107 +4808,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320673</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212365</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>382756</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237847</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>199351</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267015</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>726</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>558519</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430391</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629700</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -4921,107 +4921,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191311</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120891</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229443</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153167</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125789</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176317</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344478</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262759</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>391981</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -5034,107 +5034,107 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302981</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>200310</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359192</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>217070</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178545</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244140</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520050</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>382595</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>586427</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -5147,107 +5147,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238653</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157762</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288202</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224601</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186959</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254968</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>521</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463254</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360574</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>523650</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5260,107 +5260,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101817</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131166</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134621</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108224</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159201</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>290</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236438</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186946</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>280652</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -5373,919 +5373,123 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942545</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942545</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942545</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439238</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439238</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439238</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381783</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381783</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381783</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Nunca/ casi nunca</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>787110</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>609164</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1173935</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>40,52%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>60,43%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>471933</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>400801</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>632141</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>43,92%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1259044</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1045458</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1738965</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>30,91%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Con menos frecuencia /raramente</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>320673</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>221646</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>381593</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>237847</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>201075</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>269146</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>558519</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>434714</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>628801</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al año</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>191311</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>123202</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>231637</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>153167</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>126155</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>177375</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>344478</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>266546</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>390489</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al mes</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>302981</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>196944</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>360755</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>217070</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>184666</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>247709</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>520050</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>405897</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>588678</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces a la semana</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>238653</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>163026</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>284731</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>224601</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>189844</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>254856</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>463254</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>361210</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>524943</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>A diario</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>101817</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>64963</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>129059</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>134621</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>111004</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>158885</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>236438</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>180860</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>274787</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1942545</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1942545</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1942545</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>1439238</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>1439238</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>1439238</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>3381783</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>3381783</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>3381783</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>

--- a/data/trans_orig/P70C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>152856</t>
+          <t>163838</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132695</t>
+          <t>140657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172702</t>
+          <t>184442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125345</t>
+          <t>131734</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110289</t>
+          <t>115923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>147260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>278201</t>
+          <t>295572</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253654</t>
+          <t>270200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>324062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65017</t>
+          <t>71408</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>57303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>89870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40340</t>
+          <t>44133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115284</t>
+          <t>125033</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134036</t>
+          <t>148100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36940</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>54959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63558</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49649</t>
+          <t>58020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>89520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53612</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69392</t>
+          <t>76638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>105705</t>
+          <t>112438</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124954</t>
+          <t>135584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>44796</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>34086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54790</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>70584</t>
+          <t>77638</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55566</t>
+          <t>61867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87772</t>
+          <t>94966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>51684</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>316616</t>
+          <t>337183</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>316616</t>
+          <t>337183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316616</t>
+          <t>337183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>719995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>719995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>719995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>123548</t>
+          <t>126804</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105823</t>
+          <t>108752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143142</t>
+          <t>146449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86815</t>
+          <t>94212</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73913</t>
+          <t>80668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101876</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>210363</t>
+          <t>221016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185923</t>
+          <t>195752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234226</t>
+          <t>245197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47513</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77978</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49030</t>
+          <t>54476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39298</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111206</t>
+          <t>120879</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92680</t>
+          <t>102641</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>130430</t>
+          <t>140494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>56220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19385</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37795</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84112</t>
+          <t>88922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31691</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>66035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>77206</t>
+          <t>85357</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>69531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94482</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>43437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>40090</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>30067</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50691</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>68311</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54169</t>
+          <t>54988</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85749</t>
+          <t>86879</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>302222</t>
+          <t>319560</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302222</t>
+          <t>319560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302222</t>
+          <t>319560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>251558</t>
+          <t>272810</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251558</t>
+          <t>272810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251558</t>
+          <t>272810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>553780</t>
+          <t>592370</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>553780</t>
+          <t>592370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553780</t>
+          <t>592370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315320</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>444284</t>
+          <t>97284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>333988</t>
+          <t>100393</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>151569</t>
+          <t>82750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>470102</t>
+          <t>118167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50875</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>45192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109150</t>
+          <t>73706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69836</t>
+          <t>79596</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>64358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132091</t>
+          <t>96119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24380</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67297</t>
+          <t>53363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>40223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108880</t>
+          <t>69524</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>54108</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>44379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102991</t>
+          <t>77094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68405</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42756</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80374</t>
+          <t>58094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43161</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>44607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72647</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72647</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72647</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>562334</t>
+          <t>354814</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>562334</t>
+          <t>354814</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>562334</t>
+          <t>354814</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133780</t>
+          <t>146221</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113245</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157573</t>
+          <t>170697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>87197</t>
+          <t>95920</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>79951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103356</t>
+          <t>113103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>220977</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193767</t>
+          <t>213374</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>248798</t>
+          <t>270808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>93380</t>
+          <t>103944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73832</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122455</t>
+          <t>126719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80090</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>81590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95092</t>
+          <t>110629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>198789</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149432</t>
+          <t>174011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>203654</t>
+          <t>224958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>70229</t>
+          <t>82639</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54857</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87030</t>
+          <t>103213</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>67673</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>118796</t>
+          <t>138393</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100830</t>
+          <t>118621</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>138768</t>
+          <t>160058</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>133616</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>107980</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144915</t>
+          <t>156521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>78249</t>
+          <t>86246</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65444</t>
+          <t>71663</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>101417</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>198832</t>
+          <t>219861</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>171399</t>
+          <t>194804</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>224677</t>
+          <t>247901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122654</t>
+          <t>131028</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>85775</t>
+          <t>94931</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70646</t>
+          <t>79334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103295</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>184957</t>
+          <t>202573</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>177456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210385</t>
+          <t>232910</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>41656</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56423</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44937</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>62460</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>95553</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70010</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105559</t>
+          <t>116976</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>558811</t>
+          <t>619919</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>558811</t>
+          <t>619919</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>558811</t>
+          <t>619919</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424815</t>
+          <t>477390</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424815</t>
+          <t>477390</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424815</t>
+          <t>477390</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>983626</t>
+          <t>1097309</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>983626</t>
+          <t>1097309</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>983626</t>
+          <t>1097309</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>86785</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>68163</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>108746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>153909</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>74277</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>253424</t>
+          <t>76192</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>215515</t>
+          <t>147581</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>142002</t>
+          <t>126253</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>338616</t>
+          <t>173679</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>88722</t>
+          <t>100735</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>61216</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>113721</t>
+          <t>123269</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>42942</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>56421</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>59901</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>91479</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -4244,17 +4244,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49279</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>48134</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>46348</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>66408</t>
+          <t>72944</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>84200</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>56448</t>
+          <t>86985</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105973</t>
+          <t>125309</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38980</t>
+          <t>46017</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>79748</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>44556</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>45205</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>68744</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>116576</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>64811</t>
+          <t>97512</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>124099</t>
+          <t>137347</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>49011</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>39109</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70902</t>
+          <t>62268</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>62821</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>91530</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>239911</t>
+          <t>306800</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>239911</t>
+          <t>306800</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>239911</t>
+          <t>306800</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>613514</t>
+          <t>620526</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>613514</t>
+          <t>620526</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>613514</t>
+          <t>620526</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>787110</t>
+          <t>603392</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>607615</t>
+          <t>556662</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1178983</t>
+          <t>649833</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>471933</t>
+          <t>403311</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>398202</t>
+          <t>374437</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>627415</t>
+          <t>435290</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1259044</t>
+          <t>1006703</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1047256</t>
+          <t>951894</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1788035</t>
+          <t>1060115</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>320673</t>
+          <t>355522</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>212365</t>
+          <t>321208</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>382756</t>
+          <t>395225</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>237847</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>199351</t>
+          <t>244387</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>267015</t>
+          <t>293745</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>558519</t>
+          <t>625032</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>430391</t>
+          <t>580859</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>629700</t>
+          <t>670931</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>191311</t>
+          <t>221717</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>120891</t>
+          <t>192804</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>229443</t>
+          <t>252472</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>153167</t>
+          <t>174752</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>125789</t>
+          <t>154514</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>176317</t>
+          <t>200343</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>344478</t>
+          <t>396469</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>262759</t>
+          <t>361514</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>391981</t>
+          <t>436691</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>338816</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>200310</t>
+          <t>306297</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>359192</t>
+          <t>376713</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>242882</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>178545</t>
+          <t>218355</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>244140</t>
+          <t>270780</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>581697</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>382595</t>
+          <t>538448</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>586427</t>
+          <t>628807</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>238653</t>
+          <t>263331</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>157762</t>
+          <t>233605</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>288202</t>
+          <t>300435</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>224601</t>
+          <t>249001</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>186959</t>
+          <t>224836</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>254968</t>
+          <t>277143</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>463254</t>
+          <t>512332</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>360574</t>
+          <t>470282</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>523650</t>
+          <t>560432</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>101817</t>
+          <t>118727</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>97302</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>131166</t>
+          <t>144006</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>134621</t>
+          <t>144054</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>108224</t>
+          <t>125701</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>159201</t>
+          <t>162557</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>236438</t>
+          <t>262781</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>186946</t>
+          <t>234312</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>280652</t>
+          <t>296305</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1942545</t>
+          <t>1901505</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1942545</t>
+          <t>1901505</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1942545</t>
+          <t>1901505</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1439238</t>
+          <t>1483510</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1439238</t>
+          <t>1483510</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1439238</t>
+          <t>1483510</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3381783</t>
+          <t>3385015</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3381783</t>
+          <t>3385015</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3381783</t>
+          <t>3385015</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
